--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.02019631556212</v>
+        <v>10.72828190127884</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8226973652245</v>
+        <v>0.7836883218489813</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F2" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.95284480499367</v>
+        <v>9.742337280811473</v>
       </c>
       <c r="D3" t="n">
-        <v>17.76779233457112</v>
+        <v>2.887266254367808</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F3" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.98924370743056</v>
+        <v>9.423252102457466</v>
       </c>
       <c r="D4" t="n">
-        <v>41.00135499115988</v>
+        <v>6.66272018606348</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F4" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.54938123011603</v>
+        <v>9.189274449893855</v>
       </c>
       <c r="D5" t="n">
-        <v>50.39144093013481</v>
+        <v>8.188609151146908</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F5" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.78561146103569</v>
+        <v>5.652661862418299</v>
       </c>
       <c r="D6" t="n">
-        <v>34.27469449467218</v>
+        <v>5.56963785538423</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F6" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.18625251798566</v>
+        <v>8.48026603417267</v>
       </c>
       <c r="D7" t="n">
-        <v>51.77062206249529</v>
+        <v>8.412726085155485</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F7" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.41820535465299</v>
+        <v>7.867958370131111</v>
       </c>
       <c r="D8" t="n">
-        <v>48.89526315049793</v>
+        <v>7.945480261955915</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F8" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.89940429224835</v>
+        <v>3.233653197490357</v>
       </c>
       <c r="D9" t="n">
-        <v>20.43786242525121</v>
+        <v>3.321152644103321</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F9" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.3101828168067</v>
+        <v>7.362904707731089</v>
       </c>
       <c r="D10" t="n">
-        <v>45.84785449083231</v>
+        <v>7.450276354760251</v>
       </c>
       <c r="E10" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F10" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>59.4201597226042</v>
+        <v>9.655775954923184</v>
       </c>
       <c r="D11" t="n">
-        <v>59.95126798846173</v>
+        <v>9.742081048125032</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F11" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.60043725338348</v>
+        <v>6.110071053674816</v>
       </c>
       <c r="D12" t="n">
-        <v>37.65655128599094</v>
+        <v>6.119189583973528</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F12" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.19750882551651</v>
+        <v>8.157095184146433</v>
       </c>
       <c r="D13" t="n">
-        <v>50.17924866389355</v>
+        <v>8.154127907882703</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F13" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.23199857691762</v>
+        <v>7.187699768749114</v>
       </c>
       <c r="D14" t="n">
-        <v>44.49301136406272</v>
+        <v>7.230114346660192</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F14" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>60.57051398119223</v>
+        <v>9.842708521943738</v>
       </c>
       <c r="D15" t="n">
-        <v>60.77866555809679</v>
+        <v>9.876533153190728</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9922348038396</v>
+        <v>1.948738155623935</v>
       </c>
       <c r="F15" t="n">
-        <v>15.72587551258648</v>
+        <v>2.555454770795303</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
